--- a/diseases/d010/2010-2014.xlsx
+++ b/diseases/d010/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2149,9 +2143,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2693,9 +2684,6 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -3237,9 +3225,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3781,9 +3766,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4325,9 +4307,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4869,9 +4848,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5413,9 +5389,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5957,9 +5930,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6501,9 +6471,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7045,9 +7012,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7589,9 +7553,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -8133,9 +8094,6 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -8677,9 +8635,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -9221,9 +9176,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9765,9 +9717,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10309,9 +10258,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10853,9 +10799,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11397,9 +11340,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11941,9 +11881,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12485,9 +12422,6 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -13029,9 +12963,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -13573,9 +13504,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -14117,9 +14045,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14661,9 +14586,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15205,9 +15127,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15749,9 +15668,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -16293,9 +16209,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16837,9 +16750,6 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -17381,9 +17291,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -17925,9 +17832,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -18469,9 +18373,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -19013,9 +18914,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -19557,9 +19455,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -20101,9 +19996,6 @@
       <c r="O109" t="n">
         <v>1</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -20645,9 +20537,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -21189,9 +21078,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -21733,9 +21619,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -22277,9 +22160,6 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -22821,9 +22701,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -23365,9 +23242,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -23909,9 +23783,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -24453,9 +24324,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -24997,9 +24865,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -25541,9 +25406,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -26085,9 +25947,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -26629,9 +26488,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -27173,9 +27029,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -27717,9 +27570,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -28261,9 +28111,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -28805,9 +28652,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -29349,9 +29193,6 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -29893,9 +29734,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -30437,9 +30275,6 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -31129,9 +30964,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -31673,9 +31505,6 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -32217,9 +32046,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -32761,9 +32587,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -33303,9 +33126,6 @@
         <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" t="n">
         <v>0</v>
       </c>
       <c r="R182" t="n">
